--- a/preparations/Tableaux_TESV_RAIY.xlsx
+++ b/preparations/Tableaux_TESV_RAIY.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8044D41-5119-4668-B8F5-7D82DEDC926D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9DAF2C-0BAF-4456-83F7-610C050975E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5370" yWindow="5175" windowWidth="28800" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau 1" sheetId="2" r:id="rId1"/>
@@ -230,9 +230,6 @@
     <t>SIGNAL ID_AluControl        : std_logic_vector(3 DOWNTO 0);</t>
   </si>
   <si>
-    <t>Signal spécifiant l'opératioon que l'UAL doit effectuer en fonction du type d'instruction décodée.</t>
-  </si>
-  <si>
     <t>SIGNAL EX_PCBranch          : std_logic_vector(31 DOWNTO 0);</t>
   </si>
   <si>
@@ -560,6 +557,9 @@
   </si>
   <si>
     <t>Signal précédemment propagé contenant une donnée lue dans la mémoire de données à écrire dans le banc de registres si MEM_WB_MemtoReg = 1.</t>
+  </si>
+  <si>
+    <t>Signal spécifiant l'opération que l'UAL doit effectuer en fonction du type d'instruction décodée.</t>
   </si>
 </sst>
 </file>
@@ -744,6 +744,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -755,12 +761,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1062,12 +1062,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -1205,7 +1205,7 @@
       <c r="C11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="17" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       <c r="C12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="17" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>47</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>17</v>
@@ -1385,7 +1385,7 @@
         <v>53</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>17</v>
@@ -1396,10 +1396,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>7</v>
@@ -1410,10 +1410,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>7</v>
@@ -1424,13 +1424,13 @@
         <v>20</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,13 +1452,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1466,13 +1466,13 @@
         <v>44</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1494,13 +1494,13 @@
         <v>63</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1508,13 +1508,13 @@
         <v>42</v>
       </c>
       <c r="B33" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1522,13 +1522,13 @@
         <v>18</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1536,13 +1536,13 @@
         <v>25</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1550,13 +1550,13 @@
         <v>28</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1578,10 +1578,10 @@
         <v>35</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>52</v>
@@ -1592,13 +1592,13 @@
         <v>30</v>
       </c>
       <c r="B39" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1606,13 +1606,13 @@
         <v>29</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1620,13 +1620,13 @@
         <v>22</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1634,27 +1634,27 @@
         <v>19</v>
       </c>
       <c r="B42" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="C43" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D43" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1662,10 +1662,10 @@
         <v>16</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>42</v>
@@ -1676,10 +1676,10 @@
         <v>16</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>42</v>
@@ -1690,7 +1690,7 @@
         <v>15</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>51</v>
@@ -1704,10 +1704,10 @@
         <v>15</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>39</v>
@@ -1718,27 +1718,27 @@
         <v>21</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
-      <c r="B49" s="20" t="s">
-        <v>117</v>
+      <c r="B49" s="16" t="s">
+        <v>116</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1746,13 +1746,13 @@
         <v>62</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1760,27 +1760,27 @@
         <v>17</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B52" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="D52" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1788,13 +1788,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1802,13 +1802,13 @@
         <v>37</v>
       </c>
       <c r="B54" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1816,13 +1816,13 @@
         <v>36</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1830,10 +1830,10 @@
         <v>51</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>39</v>
@@ -1841,13 +1841,13 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B57" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>52</v>
@@ -1858,24 +1858,24 @@
         <v>50</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>34</v>
       </c>
-      <c r="B59" s="20" t="s">
-        <v>100</v>
+      <c r="B59" s="16" t="s">
+        <v>99</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>20</v>
@@ -1883,16 +1883,16 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -1900,13 +1900,13 @@
         <v>47</v>
       </c>
       <c r="B61" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -1914,13 +1914,13 @@
         <v>32</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1928,13 +1928,13 @@
         <v>46</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -1942,13 +1942,13 @@
         <v>12</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1956,13 +1956,13 @@
         <v>49</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1970,27 +1970,27 @@
         <v>45</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1998,44 +1998,44 @@
       <c r="C68" s="7"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
+      <c r="A69" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="11"/>
-      <c r="B70" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C70" s="19"/>
-      <c r="D70" s="19"/>
+      <c r="B70" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="12"/>
-      <c r="B71" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
+      <c r="B71" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="12"/>
-      <c r="B72" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C72" s="16"/>
-      <c r="D72" s="16"/>
+      <c r="B72" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="12"/>
-      <c r="B73" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C73" s="16"/>
-      <c r="D73" s="16"/>
+      <c r="B73" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B75" s="9"/>
@@ -2055,23 +2055,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="04c30d47-2f26-48be-9a1c-bfaaa643761d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AF428B9457C8246BEA697AE7148E707" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="2baae56eb1e0b61fee8271ffb68b009c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="04c30d47-2f26-48be-9a1c-bfaaa643761d" xmlns:ns4="e8a4aba6-df9f-461c-b6db-5b2e6ad93a73" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="27239d045d209dc01f255dc80d0aab0b" ns3:_="" ns4:_="">
     <xsd:import namespace="04c30d47-2f26-48be-9a1c-bfaaa643761d"/>
@@ -2280,32 +2263,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC6476D0-E80C-432C-A9C7-EC5BFD75DAAD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="04c30d47-2f26-48be-9a1c-bfaaa643761d"/>
-    <ds:schemaRef ds:uri="e8a4aba6-df9f-461c-b6db-5b2e6ad93a73"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C2ABCB-DF43-4C9A-A0EF-BE00AF75D0B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="04c30d47-2f26-48be-9a1c-bfaaa643761d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E126498F-8383-4CEA-BB3C-992584DBA55F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2322,4 +2297,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C2ABCB-DF43-4C9A-A0EF-BE00AF75D0B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC6476D0-E80C-432C-A9C7-EC5BFD75DAAD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="04c30d47-2f26-48be-9a1c-bfaaa643761d"/>
+    <ds:schemaRef ds:uri="e8a4aba6-df9f-461c-b6db-5b2e6ad93a73"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>